--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490685</v>
+        <v>121490774</v>
       </c>
       <c r="B2" t="n">
         <v>98012</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512468</v>
+        <v>512445</v>
       </c>
       <c r="R2" t="n">
-        <v>6508899</v>
+        <v>6508869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490687</v>
+        <v>121490686</v>
       </c>
       <c r="B3" t="n">
         <v>98012</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512456</v>
+        <v>512461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508880</v>
+        <v>6508894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490686</v>
+        <v>121490685</v>
       </c>
       <c r="B4" t="n">
         <v>98012</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512461</v>
+        <v>512468</v>
       </c>
       <c r="R4" t="n">
-        <v>6508894</v>
+        <v>6508899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490774</v>
+        <v>121490687</v>
       </c>
       <c r="B5" t="n">
         <v>98012</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512445</v>
+        <v>512456</v>
       </c>
       <c r="R5" t="n">
-        <v>6508869</v>
+        <v>6508880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490774</v>
+        <v>121490685</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512445</v>
+        <v>512468</v>
       </c>
       <c r="R2" t="n">
-        <v>6508869</v>
+        <v>6508899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490686</v>
+        <v>121490687</v>
       </c>
       <c r="B3" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512461</v>
+        <v>512456</v>
       </c>
       <c r="R3" t="n">
-        <v>6508894</v>
+        <v>6508880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490685</v>
+        <v>121490774</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512468</v>
+        <v>512445</v>
       </c>
       <c r="R4" t="n">
-        <v>6508899</v>
+        <v>6508869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490687</v>
+        <v>121490686</v>
       </c>
       <c r="B5" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512456</v>
+        <v>512461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508880</v>
+        <v>6508894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490685</v>
+        <v>121490687</v>
       </c>
       <c r="B2" t="n">
         <v>98015</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512468</v>
+        <v>512456</v>
       </c>
       <c r="R2" t="n">
-        <v>6508899</v>
+        <v>6508880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490687</v>
+        <v>121490774</v>
       </c>
       <c r="B3" t="n">
         <v>98015</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512456</v>
+        <v>512445</v>
       </c>
       <c r="R3" t="n">
-        <v>6508880</v>
+        <v>6508869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490774</v>
+        <v>121490685</v>
       </c>
       <c r="B4" t="n">
         <v>98015</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512445</v>
+        <v>512468</v>
       </c>
       <c r="R4" t="n">
-        <v>6508869</v>
+        <v>6508899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121490687</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121490774</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490685</v>
+        <v>121490686</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512468</v>
+        <v>512461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508899</v>
+        <v>6508894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490686</v>
+        <v>121490685</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512461</v>
+        <v>512468</v>
       </c>
       <c r="R5" t="n">
-        <v>6508894</v>
+        <v>6508899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490687</v>
+        <v>121490685</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512456</v>
+        <v>512468</v>
       </c>
       <c r="R2" t="n">
-        <v>6508880</v>
+        <v>6508899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121490774</v>
       </c>
       <c r="B3" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490686</v>
+        <v>121490687</v>
       </c>
       <c r="B4" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512461</v>
+        <v>512456</v>
       </c>
       <c r="R4" t="n">
-        <v>6508894</v>
+        <v>6508880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490685</v>
+        <v>121490686</v>
       </c>
       <c r="B5" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512468</v>
+        <v>512461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508899</v>
+        <v>6508894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490685</v>
+        <v>121490687</v>
       </c>
       <c r="B2" t="n">
         <v>98022</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512468</v>
+        <v>512456</v>
       </c>
       <c r="R2" t="n">
-        <v>6508899</v>
+        <v>6508880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490687</v>
+        <v>121490685</v>
       </c>
       <c r="B4" t="n">
         <v>98022</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512456</v>
+        <v>512468</v>
       </c>
       <c r="R4" t="n">
-        <v>6508880</v>
+        <v>6508899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490687</v>
+        <v>121490774</v>
       </c>
       <c r="B2" t="n">
         <v>98022</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512456</v>
+        <v>512445</v>
       </c>
       <c r="R2" t="n">
-        <v>6508880</v>
+        <v>6508869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490774</v>
+        <v>121490686</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512445</v>
+        <v>512461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508869</v>
+        <v>6508894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490685</v>
+        <v>121490687</v>
       </c>
       <c r="B4" t="n">
         <v>98022</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512468</v>
+        <v>512456</v>
       </c>
       <c r="R4" t="n">
-        <v>6508899</v>
+        <v>6508880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490686</v>
+        <v>121490685</v>
       </c>
       <c r="B5" t="n">
         <v>98022</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512461</v>
+        <v>512468</v>
       </c>
       <c r="R5" t="n">
-        <v>6508894</v>
+        <v>6508899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490774</v>
+        <v>121490686</v>
       </c>
       <c r="B2" t="n">
         <v>98022</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512445</v>
+        <v>512461</v>
       </c>
       <c r="R2" t="n">
-        <v>6508869</v>
+        <v>6508894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490686</v>
+        <v>121490685</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512461</v>
+        <v>512468</v>
       </c>
       <c r="R3" t="n">
-        <v>6508894</v>
+        <v>6508899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490685</v>
+        <v>121490774</v>
       </c>
       <c r="B5" t="n">
         <v>98022</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512468</v>
+        <v>512445</v>
       </c>
       <c r="R5" t="n">
-        <v>6508899</v>
+        <v>6508869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490686</v>
+        <v>121490774</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512461</v>
+        <v>512445</v>
       </c>
       <c r="R2" t="n">
-        <v>6508894</v>
+        <v>6508869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490685</v>
+        <v>121490687</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512468</v>
+        <v>512456</v>
       </c>
       <c r="R3" t="n">
-        <v>6508899</v>
+        <v>6508880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490687</v>
+        <v>121490686</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512456</v>
+        <v>512461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508880</v>
+        <v>6508894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490774</v>
+        <v>121490685</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512445</v>
+        <v>512468</v>
       </c>
       <c r="R5" t="n">
-        <v>6508869</v>
+        <v>6508899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490686</v>
+        <v>121490687</v>
       </c>
       <c r="B2" t="n">
         <v>98030</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512461</v>
+        <v>512456</v>
       </c>
       <c r="R2" t="n">
-        <v>6508894</v>
+        <v>6508880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490687</v>
+        <v>121490686</v>
       </c>
       <c r="B3" t="n">
         <v>98030</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512456</v>
+        <v>512461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508880</v>
+        <v>6508894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490685</v>
+        <v>121490774</v>
       </c>
       <c r="B4" t="n">
         <v>98030</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512468</v>
+        <v>512445</v>
       </c>
       <c r="R4" t="n">
-        <v>6508899</v>
+        <v>6508869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490774</v>
+        <v>121490685</v>
       </c>
       <c r="B5" t="n">
         <v>98030</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512445</v>
+        <v>512468</v>
       </c>
       <c r="R5" t="n">
-        <v>6508869</v>
+        <v>6508899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490687</v>
+        <v>121490774</v>
       </c>
       <c r="B2" t="n">
         <v>98030</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512456</v>
+        <v>512445</v>
       </c>
       <c r="R2" t="n">
-        <v>6508880</v>
+        <v>6508869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490686</v>
+        <v>121490687</v>
       </c>
       <c r="B3" t="n">
         <v>98030</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512461</v>
+        <v>512456</v>
       </c>
       <c r="R3" t="n">
-        <v>6508894</v>
+        <v>6508880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490774</v>
+        <v>121490685</v>
       </c>
       <c r="B4" t="n">
         <v>98030</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512445</v>
+        <v>512468</v>
       </c>
       <c r="R4" t="n">
-        <v>6508869</v>
+        <v>6508899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490685</v>
+        <v>121490686</v>
       </c>
       <c r="B5" t="n">
         <v>98030</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512468</v>
+        <v>512461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508899</v>
+        <v>6508894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490774</v>
+        <v>121490687</v>
       </c>
       <c r="B2" t="n">
         <v>98030</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512445</v>
+        <v>512456</v>
       </c>
       <c r="R2" t="n">
-        <v>6508869</v>
+        <v>6508880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490687</v>
+        <v>121490685</v>
       </c>
       <c r="B3" t="n">
         <v>98030</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512456</v>
+        <v>512468</v>
       </c>
       <c r="R3" t="n">
-        <v>6508880</v>
+        <v>6508899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490685</v>
+        <v>121490774</v>
       </c>
       <c r="B4" t="n">
         <v>98030</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512468</v>
+        <v>512445</v>
       </c>
       <c r="R4" t="n">
-        <v>6508899</v>
+        <v>6508869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 52523-2022 artfynd.xlsx
+++ b/artfynd/A 52523-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121490687</v>
+        <v>121490685</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512456</v>
+        <v>512468</v>
       </c>
       <c r="R2" t="n">
-        <v>6508880</v>
+        <v>6508899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121490685</v>
+        <v>121490686</v>
       </c>
       <c r="B3" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512468</v>
+        <v>512461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508899</v>
+        <v>6508894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121490774</v>
+        <v>121490687</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512445</v>
+        <v>512456</v>
       </c>
       <c r="R4" t="n">
-        <v>6508869</v>
+        <v>6508880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121490686</v>
+        <v>121490774</v>
       </c>
       <c r="B5" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512461</v>
+        <v>512445</v>
       </c>
       <c r="R5" t="n">
-        <v>6508894</v>
+        <v>6508869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
